--- a/data/sce_compartment_curation/2026_curated/fungal_type_vacuole_annotations.xlsx
+++ b/data/sce_compartment_curation/2026_curated/fungal_type_vacuole_annotations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M319"/>
+  <dimension ref="A1:M314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,16 +553,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>URA7</t>
+          <t>FUI1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>YBL039C</t>
+          <t>YBL042C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -614,16 +614,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FUI1</t>
+          <t>GRX7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YBR014C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -664,27 +664,27 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GRX7</t>
+          <t>FUR4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YBR021W</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -725,27 +725,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FUR4</t>
+          <t>CSG2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YBR036C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -797,16 +797,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CSG2</t>
+          <t>FIG1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YBR040W</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -858,16 +858,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIG1</t>
+          <t>ATG42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YBR139W</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -908,18 +908,18 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -969,27 +969,27 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATG42</t>
+          <t>CSH1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YBR161W</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1030,18 +1030,18 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CSH1</t>
+          <t>TOS1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YBR162C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1152,27 +1152,27 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOS1</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YBR187W</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1198,7 +1198,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1213,18 +1213,18 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1274,27 +1274,27 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>KTR4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YBR199W</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1335,27 +1335,27 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KTR4</t>
+          <t>KTR3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YBR205W</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1407,7 +1407,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1457,27 +1457,27 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KTR3</t>
+          <t>APE3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YBR286W</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1518,18 +1518,18 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1579,27 +1579,27 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Yasuhara T, et al. (1994) PMID:8175799</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>APE3</t>
+          <t>BSD2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YBR290W</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1625,7 +1625,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1640,18 +1640,18 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Yasuhara T, et al. (1994) PMID:8175799</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1701,27 +1701,27 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BSD2</t>
+          <t>COS2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YBR302C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1747,7 +1747,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1762,18 +1762,18 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1823,27 +1823,27 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COS2</t>
+          <t>RER1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YCL001W</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1869,7 +1869,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2014-01-21</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RER1</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1930,7 +1930,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1945,27 +1945,27 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2014-01-21</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2017,16 +2017,16 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>PRD1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YCL057W</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2052,7 +2052,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2067,27 +2067,27 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2014-07-08</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Hrycyna CA and Clarke S (1993) PMID:8218194</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PRD1</t>
+          <t>DFP3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YCR007C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2113,7 +2113,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2128,27 +2128,27 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2014-07-08</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hrycyna CA and Clarke S (1993) PMID:8218194</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DFP3</t>
+          <t>ADP1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YCR011C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2200,16 +2200,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADP1</t>
+          <t>FEN2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YCR028C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2261,16 +2261,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FEN2</t>
+          <t>CPR4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YCR069W</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2322,16 +2322,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CPR4</t>
+          <t>ERS1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YCR075C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2357,7 +2357,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2372,18 +2372,18 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Gao XD, et al. (2005) PMID:15885099</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2433,27 +2433,27 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Gao XD, et al. (2005) PMID:15885099</t>
+          <t>Simpkins JA, et al. (2016) PMID:27142334</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ERS1</t>
+          <t>GIT1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YCR098C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2479,7 +2479,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2494,27 +2494,27 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Simpkins JA, et al. (2016) PMID:27142334</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GIT1</t>
+          <t>YCR101C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YCR101C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2566,16 +2566,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>GRX6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YDL010W</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2601,7 +2601,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2616,18 +2616,18 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2677,18 +2677,18 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2738,27 +2738,27 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GRX6</t>
+          <t>NPC2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YDL046W</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2860,27 +2860,27 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NPC2</t>
+          <t>KNH1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YDL049C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2932,16 +2932,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KNH1</t>
+          <t>VAM6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YDL077C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2967,7 +2967,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2982,27 +2982,27 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VAM6</t>
+          <t>VCX1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YDL128W</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3048,22 +3048,22 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Cunningham KW and Fink GR (1996) PMID:8628289</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VCX1</t>
+          <t>SRF1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YDL133W</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3089,7 +3089,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3104,27 +3104,27 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Cunningham KW and Fink GR (1996) PMID:8628289</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RPP1B</t>
+          <t>AIT1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YDL130W</t>
+          <t>YDL180W</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3165,27 +3165,27 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SRF1</t>
+          <t>YDL211C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YDL211C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3226,27 +3226,27 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AIT1</t>
+          <t>COS7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YDL248W</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3287,27 +3287,27 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>RCR2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YDR003W</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3359,16 +3359,16 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COS7</t>
+          <t>RCR2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YDR003W</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3394,7 +3394,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3409,27 +3409,27 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Kota J, et al. (2007) PMID:17287526</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RCR2</t>
+          <t>ENA1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YDR040C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3470,27 +3470,27 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RCR2</t>
+          <t>PST1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YDR055W</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3516,7 +3516,7 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3531,27 +3531,27 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Kota J, et al. (2007) PMID:17287526</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ENA1</t>
+          <t>MKC7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YDR144C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3603,16 +3603,16 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PST1</t>
+          <t>YDR248C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YDR055W</t>
+          <t>YDR248C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3664,16 +3664,16 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MKC7</t>
+          <t>YDR262W</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YDR262W</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3714,27 +3714,27 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>PHM6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YDR281C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3786,16 +3786,16 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>PHM6</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YDR281C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3847,16 +3847,16 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PHM6</t>
+          <t>YDR415C</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YDR415C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3908,16 +3908,16 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PHM6</t>
+          <t>SIP1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YDR422C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3943,7 +3943,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3958,27 +3958,27 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Vincent O, et al. (2001) PMID:11331606</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RPP2B</t>
+          <t>THI74</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YDR382W</t>
+          <t>YDR438W</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4030,16 +4030,16 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>PPN1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YDR452W</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4091,16 +4091,16 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SIP1</t>
+          <t>ITR1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YDR497C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4126,7 +4126,7 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4141,27 +4141,27 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Vincent O, et al. (2001) PMID:11331606</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>THI74</t>
+          <t>FPR2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YDR519W</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4213,16 +4213,16 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PPN1</t>
+          <t>STL1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YDR536W</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4274,16 +4274,16 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ITR1</t>
+          <t>PAU10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YDR542W</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4335,16 +4335,16 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FPR2</t>
+          <t>PRB1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YEL060C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4370,7 +4370,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>TAS</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4385,27 +4385,27 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Teichert U, et al. (1989) PMID:2674123</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>STL1</t>
+          <t>SIT1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YEL065W</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4457,16 +4457,16 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PAU10</t>
+          <t>TIR1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YER011W</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4518,16 +4518,16 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PRB1</t>
+          <t>FCY22</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YER060W-A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4553,7 +4553,7 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TAS</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4568,27 +4568,27 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Teichert U, et al. (1989) PMID:2674123</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SIT1</t>
+          <t>AVT6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>YEL065W</t>
+          <t>YER119C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4629,27 +4629,27 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TIR1</t>
+          <t>YCK3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YER123W</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4675,7 +4675,7 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4690,27 +4690,27 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Hou H, et al. (2005) PMID:16301533</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FCY22</t>
+          <t>HXT10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YFL011W</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4762,16 +4762,16 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AVT6</t>
+          <t>PAU5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YFL020C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4797,7 +4797,7 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4812,27 +4812,27 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YCK3</t>
+          <t>YFL040W</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YFL040W</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4858,7 +4858,7 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4873,27 +4873,27 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Hou H, et al. (2005) PMID:16301533</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HXT10</t>
+          <t>COS4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YFL062W</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4934,27 +4934,27 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAU5</t>
+          <t>COS4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YFL062W</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5006,16 +5006,16 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>CWH41</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YGL027C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5067,16 +5067,16 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>COS4</t>
+          <t>AGA2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YGL032C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5117,27 +5117,27 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COS4</t>
+          <t>MF(ALPHA)2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YGL089C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5189,16 +5189,16 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CWH41</t>
+          <t>TPN1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YGL186C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5250,16 +5250,16 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AGA2</t>
+          <t>KEX1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YGL203C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5311,16 +5311,16 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MF(ALPHA)2</t>
+          <t>COS12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YGL263W</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5372,16 +5372,16 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TPN1</t>
+          <t>MUP1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YGR055W</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5433,16 +5433,16 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KEX1</t>
+          <t>VSB1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YGR125W</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5483,27 +5483,27 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COS12</t>
+          <t>VSB1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YGR125W</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5555,16 +5555,16 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MUP1</t>
+          <t>SNG1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YGR197C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5616,16 +5616,16 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VSB1</t>
+          <t>HSV2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YGR223C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5651,7 +5651,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5666,27 +5666,27 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Strømhaug PE, et al. (2004) PMID:15155809</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VSB1</t>
+          <t>TNA1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YGR260W</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5738,16 +5738,16 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SNG1</t>
+          <t>SCW4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YGR279C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5799,16 +5799,16 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HSV2</t>
+          <t>BGL2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YGR282C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5834,7 +5834,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5849,27 +5849,27 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Strømhaug PE, et al. (2004) PMID:15155809</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENO1</t>
+          <t>COS6</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YGR254W</t>
+          <t>YGR295C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5895,7 +5895,7 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5910,27 +5910,27 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Decker BL and Wickner WT (2006) PMID:16565073</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TNA1</t>
+          <t>COS6</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YGR295C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5971,27 +5971,27 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SCW4</t>
+          <t>YHL008C</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YHL008C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6032,27 +6032,27 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BGL2</t>
+          <t>MUP3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YHL036W</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6104,16 +6104,16 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COS6</t>
+          <t>ARN1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YHL040C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6165,16 +6165,16 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>COS6</t>
+          <t>YHL042W</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YHL042W</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6215,27 +6215,27 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>ARN2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YHL047C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6276,27 +6276,27 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MUP3</t>
+          <t>COS8</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YHL048W</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6348,16 +6348,16 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ARN1</t>
+          <t>CPR2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YHR057C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6409,16 +6409,16 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>ANS1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YHR126C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6470,16 +6470,16 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ARN2</t>
+          <t>WSS1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YHR134W</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6505,7 +6505,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6520,27 +6520,27 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2017-01-10</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Balakirev MY, et al. (2015) PMID:26349035</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COS8</t>
+          <t>DSE2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YHR143W</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6592,16 +6592,16 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CPR2</t>
+          <t>YHR173C</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YHR173C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6653,16 +6653,16 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ANS1</t>
+          <t>SMN1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>YHR126C</t>
+          <t>YHR202W</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6714,16 +6714,16 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WSS1</t>
+          <t>SMN1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YHR202W</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6749,7 +6749,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6764,27 +6764,27 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2017-01-10</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Balakirev MY, et al. (2015) PMID:26349035</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DSE2</t>
+          <t>PHO12</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YHR215W</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6825,27 +6825,27 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>TIR3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YIL011W</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6897,16 +6897,16 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ENO2</t>
+          <t>MNT3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>YHR174W</t>
+          <t>YIL014W</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6932,7 +6932,7 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6947,27 +6947,27 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Decker BL and Wickner WT (2006) PMID:16565073</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SMN1</t>
+          <t>YIL067C</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YIL067C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7008,27 +7008,27 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SMN1</t>
+          <t>AVT7</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YIL088C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7069,27 +7069,27 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PHO12</t>
+          <t>AVT7</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YIL088C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7115,7 +7115,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7130,27 +7130,27 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TIR3</t>
+          <t>AVT7</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YIL088C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7176,7 +7176,7 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7191,27 +7191,27 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Nishida I, et al. (2016) PMID:27246536</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MNT3</t>
+          <t>YIL089W</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YIL089W</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7263,16 +7263,16 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>SGA1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YIL099W</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7298,7 +7298,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7313,27 +7313,27 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Pugh TA, et al. (1989) PMID:2493265</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AVT7</t>
+          <t>SGA1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YIL099W</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7385,16 +7385,16 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AVT7</t>
+          <t>AXL2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YIL140W</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7420,7 +7420,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7435,27 +7435,27 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AVT7</t>
+          <t>AIM20</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YIL158W</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7481,7 +7481,7 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7496,27 +7496,27 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nishida I, et al. (2016) PMID:27246536</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>SUC2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YIL162W</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7568,16 +7568,16 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SGA1</t>
+          <t>SOA1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YIL166C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7603,7 +7603,7 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7618,27 +7618,27 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Pugh TA, et al. (1989) PMID:2493265</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SGA1</t>
+          <t>VTH1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YIL173W</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7690,16 +7690,16 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AXL2</t>
+          <t>VLD1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YIR014W</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7740,27 +7740,27 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AIM20</t>
+          <t>FLO11</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YIR019C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7801,27 +7801,27 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SUC2</t>
+          <t>DAL4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YIR028W</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7873,16 +7873,16 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOA1</t>
+          <t>PAU15</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YIR041W</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7934,16 +7934,16 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>VTH1</t>
+          <t>IRC18</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YJL037W</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7995,16 +7995,16 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VLD1</t>
+          <t>IRC8</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>YIR014W</t>
+          <t>YJL051W</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8045,27 +8045,27 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FLO11</t>
+          <t>YHC3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YJL059W</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8091,7 +8091,7 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8106,27 +8106,27 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Pearce DA, et al. (1999) PMID:10319861</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DAL4</t>
+          <t>YHC3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YJL059W</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8152,7 +8152,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8167,27 +8167,27 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Croopnick JB, et al. (1998) PMID:9753630</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PAU15</t>
+          <t>PRY1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YJL079C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8228,27 +8228,27 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IRC18</t>
+          <t>PHS1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YJL097W</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8274,7 +8274,7 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8289,27 +8289,27 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IRC8</t>
+          <t>PHS1</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YJL097W</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8350,27 +8350,27 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YHC3</t>
+          <t>PHS1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YJL097W</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8396,7 +8396,7 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8411,27 +8411,27 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Pearce DA, et al. (1999) PMID:10319861</t>
+          <t>Hazbun TR, et al. (2003) PMID:14690591</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YHC3</t>
+          <t>NCA3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YJL116C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8457,7 +8457,7 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8472,27 +8472,27 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Croopnick JB, et al. (1998) PMID:9753630</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PRY1</t>
+          <t>YJL132W</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YJL132W</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8533,27 +8533,27 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PHS1</t>
+          <t>SNA3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YJL151C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8594,27 +8594,27 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-01-21</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PHS1</t>
+          <t>SNA3</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YJL151C</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8640,7 +8640,7 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8655,27 +8655,27 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PHS1</t>
+          <t>CIS3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YJL158C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8716,27 +8716,27 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Hazbun TR, et al. (2003) PMID:14690591</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NCA3</t>
+          <t>PIR5</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YJL160C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8788,16 +8788,16 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>CPS1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YJL172W</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8849,16 +8849,16 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SNA3</t>
+          <t>KRE9</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YJL174W</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8884,7 +8884,7 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8899,27 +8899,27 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2014-01-21</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SNA3</t>
+          <t>ATG27</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YJL178C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8945,7 +8945,7 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8960,27 +8960,27 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CIS3</t>
+          <t>HXT9</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YJL219W</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9032,16 +9032,16 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PIR5</t>
+          <t>VTH2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YJL222W</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9093,16 +9093,16 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CPS1</t>
+          <t>PAU1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>YJL172W</t>
+          <t>YJL223C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9154,16 +9154,16 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>KRE9</t>
+          <t>AVT1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YJR001W</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9189,7 +9189,7 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9204,27 +9204,27 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ATG27</t>
+          <t>AVT1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YJR001W</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9250,7 +9250,7 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9265,27 +9265,27 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Nishida I, et al. (2016) PMID:27246536</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HXT9</t>
+          <t>SAG1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YJR004C</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9337,16 +9337,16 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>VTH2</t>
+          <t>GEF1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YJR040W</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9372,7 +9372,7 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9387,27 +9387,27 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>López-Rodríguez A, et al. (2007) PMID:17662057</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PAU1</t>
+          <t>KCH1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YJR054W</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9448,27 +9448,27 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AVT1</t>
+          <t>URA8</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YJR103W</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9494,7 +9494,7 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9509,27 +9509,27 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>AVT1</t>
+          <t>MET5</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YJR137C</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9555,7 +9555,7 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9570,27 +9570,27 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nishida I, et al. (2016) PMID:27246536</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SAG1</t>
+          <t>DAL5</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YJR152W</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9642,16 +9642,16 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GEF1</t>
+          <t>MPH3</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YJR160C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9677,7 +9677,7 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9692,27 +9692,27 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>López-Rodríguez A, et al. (2007) PMID:17662057</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KCH1</t>
+          <t>COS5</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YJR161C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9764,16 +9764,16 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>URA8</t>
+          <t>TUL1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YKL034W</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9825,16 +9825,16 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MET5</t>
+          <t>CWP1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YKL096W</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9886,16 +9886,16 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DAL5</t>
+          <t>APE1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YKL103C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9921,7 +9921,7 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9936,27 +9936,27 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Klionsky DJ, et al. (1992) PMID:1400574</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MPH3</t>
+          <t>SSH4</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YKL124W</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9982,7 +9982,7 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9997,27 +9997,27 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Kota J, et al. (2007) PMID:17287526</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>COS5</t>
+          <t>AVT3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YKL146W</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10043,7 +10043,7 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10058,27 +10058,27 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Nishida I, et al. (2016) PMID:27246536</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TUL1</t>
+          <t>MCD4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YKL165C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10104,7 +10104,7 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10119,27 +10119,27 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Packeiser AN, et al. (1999) PMID:10514566</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CWP1</t>
+          <t>YKT6</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YKL196C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10165,7 +10165,7 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10180,27 +10180,27 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Dietrich LE, et al. (2005) PMID:15723044</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>APE1</t>
+          <t>STE6</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YKL209C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10226,7 +10226,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10241,27 +10241,27 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Klionsky DJ, et al. (1992) PMID:1400574</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SSH4</t>
+          <t>JEN1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YKL217W</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10287,7 +10287,7 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10302,27 +10302,27 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Kota J, et al. (2007) PMID:17287526</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AVT3</t>
+          <t>FRE2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YKL220C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10348,7 +10348,7 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10363,27 +10363,27 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Nishida I, et al. (2016) PMID:27246536</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MCD4</t>
+          <t>PAU16</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YKL224C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10409,7 +10409,7 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10424,27 +10424,27 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Packeiser AN, et al. (1999) PMID:10514566</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>YKT6</t>
+          <t>PRY2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YKR013W</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10470,7 +10470,7 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10485,27 +10485,27 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Dietrich LE, et al. (2005) PMID:15723044</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>STE6</t>
+          <t>UIP5</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YKR044W</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10557,16 +10557,16 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JEN1</t>
+          <t>PTR2</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YKR093W</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10618,16 +10618,16 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FRE2</t>
+          <t>PAU17</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YLL025W</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10679,16 +10679,16 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PAU16</t>
+          <t>FPS1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YLL043W</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10729,27 +10729,27 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PRY2</t>
+          <t>FPS1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YLL043W</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10790,27 +10790,27 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>UIP5</t>
+          <t>YBT1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YLL048C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10836,7 +10836,7 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10851,27 +10851,27 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Ortiz DF, et al. (1997) PMID:9182565</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PTR2</t>
+          <t>FRE6</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YLL051C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10923,16 +10923,16 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PAU17</t>
+          <t>FRE6</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YLL051C</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10973,27 +10973,27 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FPS1</t>
+          <t>YLR001C</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YLR001C</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11034,27 +11034,27 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>FPS1</t>
+          <t>PAU23</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YLR037C</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11106,16 +11106,16 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>YBT1</t>
+          <t>NFG1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YLR042C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11141,7 +11141,7 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11156,27 +11156,27 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Ortiz DF, et al. (1997) PMID:9182565</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>FRE6</t>
+          <t>YLR046C</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YLR046C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11228,16 +11228,16 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>FRE6</t>
+          <t>LCL2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YLR104W</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11278,27 +11278,27 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>CCW12</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YLR110C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11350,16 +11350,16 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PAU23</t>
+          <t>NCW2</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YLR194C</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11411,16 +11411,16 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>NFG1</t>
+          <t>CRR1</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YLR213C</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11472,16 +11472,16 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>CCC1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YLR220W</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11507,7 +11507,7 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11522,27 +11522,27 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LCL2</t>
+          <t>SSP120</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YLR250W</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11594,16 +11594,16 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CCW12</t>
+          <t>CTS1</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YLR286C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11655,16 +11655,16 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>NCW2</t>
+          <t>YLR297W</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YLR297W</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11705,27 +11705,27 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>CRR1</t>
+          <t>ECM38</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YLR299W</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11751,7 +11751,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11766,27 +11766,27 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Jaspers CJ and Penninckx MJ (1984) PMID:6143574</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CCC1</t>
+          <t>EXG1</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YLR300W</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11812,7 +11812,7 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11827,27 +11827,27 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SSP120</t>
+          <t>MID2</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YLR332W</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11899,16 +11899,16 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CTS1</t>
+          <t>GAS2</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YLR343W</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11960,16 +11960,16 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>DCR2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YLR361C</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12010,27 +12010,27 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ECM38</t>
+          <t>VPS33</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YLR396C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12076,22 +12076,22 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Jaspers CJ and Penninckx MJ (1984) PMID:6143574</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EXG1</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12143,16 +12143,16 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MID2</t>
+          <t>INA1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YLR413W</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12204,16 +12204,16 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GAS2</t>
+          <t>ECM7</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YLR443W</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12265,16 +12265,16 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DCR2</t>
+          <t>PAU4</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YLR461W</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12326,16 +12326,16 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>VPS33</t>
+          <t>YPT7</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YML001W</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12387,16 +12387,16 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>ERV25</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YML012W</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12448,16 +12448,16 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>INA1</t>
+          <t>PRM6</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YML047C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12509,16 +12509,16 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ECM7</t>
+          <t>SMA2</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YML066C</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12570,16 +12570,16 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PAU4</t>
+          <t>MDM1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YML104C</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12631,16 +12631,16 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>YPT7</t>
+          <t>PHO84</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YML123C</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12666,7 +12666,7 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12681,27 +12681,27 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ERV25</t>
+          <t>COS3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YML132W</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12753,16 +12753,16 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PRM6</t>
+          <t>COS3</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YML132W</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12803,27 +12803,27 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SMA2</t>
+          <t>COS3</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YML132W</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12849,7 +12849,7 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12864,27 +12864,27 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Mitsui K, et al. (2004) PMID:14718542</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MDM1</t>
+          <t>HXT2</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YMR011W</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12936,16 +12936,16 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PHO84</t>
+          <t>FET3</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YMR058W</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12997,16 +12997,16 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>COS3</t>
+          <t>YMR155W</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YMR155W</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -13058,16 +13058,16 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>COS3</t>
+          <t>GAS3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YMR215W</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -13108,27 +13108,27 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>COS3</t>
+          <t>FMP42</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YMR221C</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -13154,7 +13154,7 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -13169,27 +13169,27 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Mitsui K, et al. (2004) PMID:14718542</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HXT2</t>
+          <t>ZRC1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>YMR011W</t>
+          <t>YMR243C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13215,7 +13215,7 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13230,27 +13230,27 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Li L and Kaplan J (1998) PMID:9712830</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FET3</t>
+          <t>YMR244W</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YMR244W</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -13302,16 +13302,16 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -13363,16 +13363,16 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GAS3</t>
+          <t>HOR7</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13424,16 +13424,16 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>FMP42</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13474,27 +13474,27 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ZRC1</t>
+          <t>PRC1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YMR297W</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13540,22 +13540,22 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Li L and Kaplan J (1998) PMID:9712830</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>PRC1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YMR297W</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13596,27 +13596,27 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>FET4</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YMR319C</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -13668,16 +13668,16 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HOR7</t>
+          <t>SPO1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YNL012W</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13729,16 +13729,16 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YNL019C</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YNL019C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13790,16 +13790,16 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PRC1</t>
+          <t>YNL058C</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YNL058C</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13825,7 +13825,7 @@
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13840,27 +13840,27 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PRC1</t>
+          <t>AQR1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YNL065W</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13901,27 +13901,27 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>FET4</t>
+          <t>AVT4</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YNL101W</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13947,7 +13947,7 @@
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13962,27 +13962,27 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SPO1</t>
+          <t>YNL115C</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YNL115C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -14023,27 +14023,27 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>NRK1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YNL129W</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -14095,16 +14095,16 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>TDA7</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YNL176C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -14156,16 +14156,16 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>AQR1</t>
+          <t>TDA7</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YNL176C</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -14191,7 +14191,7 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14206,27 +14206,27 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>AVT4</t>
+          <t>PPN2</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YNL217W</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -14252,7 +14252,7 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14267,27 +14267,27 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>PPN2</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YNL217W</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -14313,7 +14313,7 @@
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14328,27 +14328,27 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>NRK1</t>
+          <t>KEX2</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YNL238W</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -14400,16 +14400,16 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TDA7</t>
+          <t>BOR1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YNL275W</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14435,7 +14435,7 @@
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14450,27 +14450,27 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Decker BL and Wickner WT (2006) PMID:16565073</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TDA7</t>
+          <t>PRM1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YNL279W</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14496,7 +14496,7 @@
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14511,27 +14511,27 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PPN2</t>
+          <t>WSC2</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YNL283C</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14572,27 +14572,27 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PPN2</t>
+          <t>CLA4</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YNL298W</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14638,22 +14638,22 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Bartholomew CR and Hardy CF (2009) PMID:19218422</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>KEX2</t>
+          <t>BXI1</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YNL305C</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14694,27 +14694,27 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>BOR1</t>
+          <t>BXI1</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YNL305C</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14740,7 +14740,7 @@
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14755,27 +14755,27 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Decker BL and Wickner WT (2006) PMID:16565073</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PRM1</t>
+          <t>BXI1</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>YNL279W</t>
+          <t>YNL305C</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14801,7 +14801,7 @@
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14816,27 +14816,27 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Büttner S, et al. (2011) PMID:21673659</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>WSC2</t>
+          <t>BXI1</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YNL305C</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14862,7 +14862,7 @@
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14877,27 +14877,27 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Cebulski J, et al. (2011) PMID:21673967</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CLA4</t>
+          <t>HXT14</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YNL318C</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14923,7 +14923,7 @@
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14938,27 +14938,27 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Bartholomew CR and Hardy CF (2009) PMID:19218422</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>BXI1</t>
+          <t>YNL320W</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YNL320W</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14999,27 +14999,27 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>BXI1</t>
+          <t>VNX1</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YNL321W</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -15045,7 +15045,7 @@
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15060,27 +15060,27 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Cagnac O, et al. (2007) PMID:17588950</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>BXI1</t>
+          <t>KRE1</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YNL322C</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -15106,7 +15106,7 @@
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15121,27 +15121,27 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Büttner S, et al. (2011) PMID:21673659</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>BXI1</t>
+          <t>PFA3</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YNL326C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -15187,22 +15187,22 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Cebulski J, et al. (2011) PMID:21673967</t>
+          <t>Hou H, et al. (2005) PMID:16301533</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HXT14</t>
+          <t>PFA3</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YNL326C</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -15243,27 +15243,27 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>PFA3</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YNL326C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -15289,7 +15289,7 @@
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IMP</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15304,27 +15304,27 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Hou H, et al. (2005) PMID:16301533</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>VNX1</t>
+          <t>PFA3</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YNL326C</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -15350,7 +15350,7 @@
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15365,27 +15365,27 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Cagnac O, et al. (2007) PMID:17588950</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>KRE1</t>
+          <t>EGT2</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YNL327W</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -15437,16 +15437,16 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PFA3</t>
+          <t>COS1</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YNL336W</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15472,7 +15472,7 @@
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -15487,27 +15487,27 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Hou H, et al. (2005) PMID:16301533</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PFA3</t>
+          <t>COS1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YNL336W</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -15559,16 +15559,16 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PFA3</t>
+          <t>ATO2</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YNR002C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15594,7 +15594,7 @@
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
-          <t>IMP</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -15609,27 +15609,27 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Hou H, et al. (2005) PMID:16301533</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PFA3</t>
+          <t>CPR8</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YNR028W</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15670,27 +15670,27 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>EGT2</t>
+          <t>HOL1</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YNR055C</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15742,16 +15742,16 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>COS1</t>
+          <t>YNR061C</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YNR061C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15777,7 +15777,7 @@
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -15792,27 +15792,27 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>COS1</t>
+          <t>YNR061C</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YNR061C</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15864,16 +15864,16 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ATO2</t>
+          <t>YNR066C</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YNR066C</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15925,16 +15925,16 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>CPR8</t>
+          <t>HXT17</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YNR072W</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15975,27 +15975,27 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>HOL1</t>
+          <t>PAU6</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YNR076W</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -16047,16 +16047,16 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>IZH2</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YOL002C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -16082,7 +16082,7 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16097,27 +16097,27 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>CSI2</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YOL007C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -16158,27 +16158,27 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>CSI2</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YOL007C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -16204,7 +16204,7 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -16219,27 +16219,27 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Sundin BA, et al. (2004) PMID:15282802</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>HXT17</t>
+          <t>CSI2</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YOL007C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -16280,27 +16280,27 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PAU6</t>
+          <t>PLB3</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YOL011W</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -16352,16 +16352,16 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>IZH2</t>
+          <t>TOS7</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YOL019W</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -16402,27 +16402,27 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>CSI2</t>
+          <t>DDR2</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16474,16 +16474,16 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CSI2</t>
+          <t>DDR2</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -16509,7 +16509,7 @@
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -16524,27 +16524,27 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Sundin BA, et al. (2004) PMID:15282802</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>CSI2</t>
+          <t>PHM7</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YOL084W</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -16596,16 +16596,16 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PLB3</t>
+          <t>IZH4</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YOL101C</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -16657,16 +16657,16 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>TOS7</t>
+          <t>ITR2</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YOL103W</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -16707,27 +16707,27 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DDR2</t>
+          <t>WSC3</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YOL105C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16779,16 +16779,16 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DDR2</t>
+          <t>SMF1</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YOL122C</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16829,27 +16829,27 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PHM7</t>
+          <t>GAS4</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YOL132W</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16890,27 +16890,27 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>IZH4</t>
+          <t>RTC1</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YOL138C</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16951,27 +16951,27 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ITR2</t>
+          <t>ZPS1</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YOL154W</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -17012,27 +17012,27 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>WSC3</t>
+          <t>ENB1</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YOL158C</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -17084,16 +17084,16 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SMF1</t>
+          <t>PAU20</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YOL161C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -17145,16 +17145,16 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>GAS4</t>
+          <t>SLG1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YOR008C</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -17206,16 +17206,16 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>RTC1</t>
+          <t>TIR4</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YOR009W</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -17256,27 +17256,27 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ZPS1</t>
+          <t>TIR2</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YOR010C</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -17317,27 +17317,27 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>ENB1</t>
+          <t>AKR2</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YOR034C</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -17389,16 +17389,16 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PAU20</t>
+          <t>RSB1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YOR049C</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -17450,16 +17450,16 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SLG1</t>
+          <t>YVC1</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YOR087W</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17485,7 +17485,7 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -17500,27 +17500,27 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Palmer CP, et al. (2001) PMID:11427713</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>TIR4</t>
+          <t>YVC1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YOR087W</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17546,7 +17546,7 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -17561,27 +17561,27 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Denis V and Cyert MS (2002) PMID:11781332</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>TIR2</t>
+          <t>KTR1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>YOR010C</t>
+          <t>YOR099W</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -17633,16 +17633,16 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>AKR2</t>
+          <t>RIO1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YOR119C</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -17668,7 +17668,7 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -17683,27 +17683,27 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2021-11-22</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Iacovella MG, et al. (2018) PMID:30011030</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>RSB1</t>
+          <t>SPR1</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YOR190W</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17755,16 +17755,16 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>YVC1</t>
+          <t>THI72</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YOR192C</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17790,7 +17790,7 @@
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -17805,27 +17805,27 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Palmer CP, et al. (2001) PMID:11427713</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>YVC1</t>
+          <t>SPR2</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YOR214C</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -17851,7 +17851,7 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17866,27 +17866,27 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Denis V and Cyert MS (2002) PMID:11781332</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>KTR1</t>
+          <t>SRL1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YOR247W</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17927,27 +17927,27 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>RIO1</t>
+          <t>VPH1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YOR270C</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -17988,27 +17988,27 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>2021-11-22</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Iacovella MG, et al. (2018) PMID:30011030</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>SPR1</t>
+          <t>MPD1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YOR288C</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -18049,27 +18049,27 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>THI72</t>
+          <t>YOR292C</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>YOR192C</t>
+          <t>YOR292C</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -18110,27 +18110,27 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SPR2</t>
+          <t>RAX1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YOR301W</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -18182,16 +18182,16 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SRL1</t>
+          <t>COT1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YOR316C</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -18217,7 +18217,7 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18232,27 +18232,27 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Li L and Kaplan J (1998) PMID:9712830</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>VPH1</t>
+          <t>PDR10</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YOR328W</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -18278,7 +18278,7 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -18293,27 +18293,27 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MPD1</t>
+          <t>FRE3</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YOR381W</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -18354,27 +18354,27 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>FIT2</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YOR382W</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18415,27 +18415,27 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>RAX1</t>
+          <t>FIT3</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YOR383C</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18487,16 +18487,16 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>COT1</t>
+          <t>KTR6</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YPL053C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18522,7 +18522,7 @@
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -18537,27 +18537,27 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Li L and Kaplan J (1998) PMID:9712830</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PDR10</t>
+          <t>SUR1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YPL057C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -18609,16 +18609,16 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>FRE3</t>
+          <t>RNY1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YPL123C</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -18644,7 +18644,7 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -18659,27 +18659,27 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2014-01-22</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Shcherbik N (2013) PMID:24102742</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>FIT2</t>
+          <t>PEP4</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YPL154C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -18731,16 +18731,16 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>FIT3</t>
+          <t>PEP4</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YPL154C</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -18766,7 +18766,7 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18781,27 +18781,27 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>KTR6</t>
+          <t>PRM4</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YPL156C</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -18853,16 +18853,16 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>SUR1</t>
+          <t>SVS1</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YPL163C</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -18903,27 +18903,27 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>RNY1</t>
+          <t>TRE1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YPL176C</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -18964,27 +18964,27 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2014-01-22</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Shcherbik N (2013) PMID:24102742</t>
+          <t>Stimpson HE, et al. (2006) PMID:16456538</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PEP4</t>
+          <t>TRE1</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YPL176C</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -19036,16 +19036,16 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PEP4</t>
+          <t>FLC1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YPL221W</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -19071,7 +19071,7 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -19086,27 +19086,27 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PRM4</t>
+          <t>VMA11</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YPL234C</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -19132,7 +19132,7 @@
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -19147,27 +19147,27 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>SVS1</t>
+          <t>DIP5</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YPL265W</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -19208,27 +19208,27 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>TRE1</t>
+          <t>PAU22</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YPL282C</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -19254,7 +19254,7 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -19269,27 +19269,27 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Stimpson HE, et al. (2006) PMID:16456538</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>TRE1</t>
+          <t>ATH1</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YPR026W</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -19315,7 +19315,7 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IMP</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -19330,27 +19330,27 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Destruelle M, et al. (1995) PMID:7502577</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>FLC1</t>
+          <t>ERV2</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YPR037C</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -19391,27 +19391,27 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>VMA11</t>
+          <t>OPY2</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YPR075C</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -19437,7 +19437,7 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -19452,27 +19452,27 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DIP5</t>
+          <t>TDA6</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YPR157W</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -19524,16 +19524,16 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PAU22</t>
+          <t>OPT2</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>YPL282C</t>
+          <t>YPR194C</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -19578,311 +19578,6 @@
         </is>
       </c>
       <c r="M314" t="inlineStr">
-        <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="1" t="n">
-        <v>319</v>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>ATH1</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>YPR026W</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>located in</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>GO:0000324</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>fungal-type vacuole</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>cellular component</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>IMP</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>manually curated</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t>2013-08-07</t>
-        </is>
-      </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>Destruelle M, et al. (1995) PMID:7502577</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="n">
-        <v>320</v>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>ERV2</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>YPR037C</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>located in</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>GO:0000324</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>fungal-type vacuole</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>cellular component</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>HDA</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>manually curated</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t>2018-11-20</t>
-        </is>
-      </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="1" t="n">
-        <v>321</v>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>OPY2</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>YPR075C</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>located in</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>GO:0000324</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>fungal-type vacuole</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>cellular component</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>HDA</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>manually curated</t>
-        </is>
-      </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t>2018-11-19</t>
-        </is>
-      </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="1" t="n">
-        <v>322</v>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>TDA6</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>YPR157W</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>located in</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>GO:0000324</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>fungal-type vacuole</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>cellular component</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>HDA</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>manually curated</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>2018-11-20</t>
-        </is>
-      </c>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="1" t="n">
-        <v>323</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>OPT2</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>YPR194C</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>located in</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>GO:0000324</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>fungal-type vacuole</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>cellular component</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>HDA</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>manually curated</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
-      </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t>2018-11-20</t>
-        </is>
-      </c>
-      <c r="M319" t="inlineStr">
         <is>
           <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>

--- a/data/sce_compartment_curation/2026_curated/fungal_type_vacuole_annotations.xlsx
+++ b/data/sce_compartment_curation/2026_curated/fungal_type_vacuole_annotations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M314"/>
+  <dimension ref="A1:M315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,16 +553,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FUI1</t>
+          <t>URA7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>YBL042C</t>
+          <t>YBL039C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -614,16 +614,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GRX7</t>
+          <t>FUI1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>YBR014C</t>
+          <t>YBL042C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -664,27 +664,27 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FUR4</t>
+          <t>GRX7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YBR021W</t>
+          <t>YBR014C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -725,27 +725,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSG2</t>
+          <t>FUR4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YBR036C</t>
+          <t>YBR021W</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -797,16 +797,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIG1</t>
+          <t>CSG2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>YBR040W</t>
+          <t>YBR036C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -858,16 +858,16 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATG42</t>
+          <t>FIG1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>YBR139W</t>
+          <t>YBR040W</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -908,18 +908,18 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -969,27 +969,27 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CSH1</t>
+          <t>ATG42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>YBR161W</t>
+          <t>YBR139W</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1030,18 +1030,18 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1091,27 +1091,27 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOS1</t>
+          <t>CSH1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YBR162C</t>
+          <t>YBR161W</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1152,27 +1152,27 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>TOS1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>YBR187W</t>
+          <t>YBR162C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1198,7 +1198,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1213,18 +1213,18 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1274,27 +1274,27 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KTR4</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>YBR199W</t>
+          <t>YBR187W</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1335,27 +1335,27 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KTR3</t>
+          <t>KTR4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>YBR205W</t>
+          <t>YBR199W</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1407,7 +1407,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1457,27 +1457,27 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APE3</t>
+          <t>KTR3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>YBR286W</t>
+          <t>YBR205W</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1518,18 +1518,18 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1579,27 +1579,27 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Yasuhara T, et al. (1994) PMID:8175799</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BSD2</t>
+          <t>APE3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>YBR290W</t>
+          <t>YBR286W</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1625,7 +1625,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1640,18 +1640,18 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Yasuhara T, et al. (1994) PMID:8175799</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1701,27 +1701,27 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COS2</t>
+          <t>BSD2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YBR302C</t>
+          <t>YBR290W</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1747,7 +1747,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1762,18 +1762,18 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1823,27 +1823,27 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RER1</t>
+          <t>COS2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YCL001W</t>
+          <t>YBR302C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1869,7 +1869,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2014-01-21</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>RER1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>YCL021W-A</t>
+          <t>YCL001W</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1930,7 +1930,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1945,27 +1945,27 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2014-01-21</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YCL048W-A</t>
+          <t>YCL021W-A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2017,16 +2017,16 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PRD1</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YCL057W</t>
+          <t>YCL048W-A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2052,7 +2052,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2067,27 +2067,27 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2014-07-08</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Hrycyna CA and Clarke S (1993) PMID:8218194</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DFP3</t>
+          <t>PRD1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YCR007C</t>
+          <t>YCL057W</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2113,7 +2113,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2128,27 +2128,27 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2014-07-08</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Hrycyna CA and Clarke S (1993) PMID:8218194</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ADP1</t>
+          <t>DFP3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YCR011C</t>
+          <t>YCR007C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2200,16 +2200,16 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FEN2</t>
+          <t>ADP1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YCR028C</t>
+          <t>YCR011C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2261,16 +2261,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CPR4</t>
+          <t>FEN2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YCR069W</t>
+          <t>YCR028C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2322,16 +2322,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ERS1</t>
+          <t>CPR4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YCR075C</t>
+          <t>YCR069W</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2357,7 +2357,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2372,18 +2372,18 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Gao XD, et al. (2005) PMID:15885099</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2433,27 +2433,27 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Simpkins JA, et al. (2016) PMID:27142334</t>
+          <t>Gao XD, et al. (2005) PMID:15885099</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GIT1</t>
+          <t>ERS1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YCR098C</t>
+          <t>YCR075C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2479,7 +2479,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2494,27 +2494,27 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Simpkins JA, et al. (2016) PMID:27142334</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>GIT1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YCR101C</t>
+          <t>YCR098C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2566,16 +2566,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GRX6</t>
+          <t>YCR101C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YDL010W</t>
+          <t>YCR101C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2601,7 +2601,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2616,18 +2616,18 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2677,18 +2677,18 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2738,27 +2738,27 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NPC2</t>
+          <t>GRX6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YDL046W</t>
+          <t>YDL010W</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2860,27 +2860,27 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KNH1</t>
+          <t>NPC2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YDL049C</t>
+          <t>YDL046W</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2932,16 +2932,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VAM6</t>
+          <t>KNH1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YDL077C</t>
+          <t>YDL049C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2967,7 +2967,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2982,27 +2982,27 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VCX1</t>
+          <t>VAM6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YDL128W</t>
+          <t>YDL077C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3048,22 +3048,22 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Cunningham KW and Fink GR (1996) PMID:8628289</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SRF1</t>
+          <t>VCX1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YDL133W</t>
+          <t>YDL128W</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3089,7 +3089,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3104,27 +3104,27 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Cunningham KW and Fink GR (1996) PMID:8628289</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AIT1</t>
+          <t>SRF1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YDL180W</t>
+          <t>YDL133W</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3165,27 +3165,27 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>AIT1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YDL211C</t>
+          <t>YDL180W</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3237,16 +3237,16 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COS7</t>
+          <t>YDL211C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YDL248W</t>
+          <t>YDL211C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3287,27 +3287,27 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RCR2</t>
+          <t>COS7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YDR003W</t>
+          <t>YDL248W</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3348,18 +3348,18 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3409,27 +3409,27 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Kota J, et al. (2007) PMID:17287526</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ENA1</t>
+          <t>RCR2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YDR040C</t>
+          <t>YDR003W</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3455,7 +3455,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3470,27 +3470,27 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Kota J, et al. (2007) PMID:17287526</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PST1</t>
+          <t>ENA1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YDR055W</t>
+          <t>YDR040C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3542,16 +3542,16 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MKC7</t>
+          <t>PST1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YDR144C</t>
+          <t>YDR055W</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3603,16 +3603,16 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>MKC7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YDR248C</t>
+          <t>YDR144C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3664,16 +3664,16 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YDR248C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YDR262W</t>
+          <t>YDR248C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3714,27 +3714,27 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PHM6</t>
+          <t>YDR262W</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YDR281C</t>
+          <t>YDR262W</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3775,18 +3775,18 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3836,27 +3836,27 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>PHM6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>YDR415C</t>
+          <t>YDR281C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3897,27 +3897,27 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SIP1</t>
+          <t>YDR415C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>YDR422C</t>
+          <t>YDR415C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3943,7 +3943,7 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3958,27 +3958,27 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Vincent O, et al. (2001) PMID:11331606</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>THI74</t>
+          <t>SIP1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YDR438W</t>
+          <t>YDR422C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4004,7 +4004,7 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4019,27 +4019,27 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Vincent O, et al. (2001) PMID:11331606</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PPN1</t>
+          <t>THI74</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YDR452W</t>
+          <t>YDR438W</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4091,16 +4091,16 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ITR1</t>
+          <t>PPN1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>YDR497C</t>
+          <t>YDR452W</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4152,16 +4152,16 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FPR2</t>
+          <t>ITR1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YDR519W</t>
+          <t>YDR497C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4213,16 +4213,16 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>STL1</t>
+          <t>FPR2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YDR536W</t>
+          <t>YDR519W</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4274,16 +4274,16 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PAU10</t>
+          <t>STL1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YDR542W</t>
+          <t>YDR536W</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4335,16 +4335,16 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PRB1</t>
+          <t>PAU10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YEL060C</t>
+          <t>YDR542W</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4370,7 +4370,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TAS</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4385,27 +4385,27 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Teichert U, et al. (1989) PMID:2674123</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SIT1</t>
+          <t>PRB1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>YEL065W</t>
+          <t>YEL060C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4431,7 +4431,7 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>TAS</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4446,27 +4446,27 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Teichert U, et al. (1989) PMID:2674123</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TIR1</t>
+          <t>SIT1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YER011W</t>
+          <t>YEL065W</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4518,16 +4518,16 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FCY22</t>
+          <t>TIR1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>YER060W-A</t>
+          <t>YER011W</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4579,16 +4579,16 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AVT6</t>
+          <t>FCY22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>YER119C</t>
+          <t>YER060W-A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4629,27 +4629,27 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>YCK3</t>
+          <t>AVT6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>YER123W</t>
+          <t>YER119C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Hou H, et al. (2005) PMID:16301533</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HXT10</t>
+          <t>YCK3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YFL011W</t>
+          <t>YER123W</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4736,7 +4736,7 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4751,27 +4751,27 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Hou H, et al. (2005) PMID:16301533</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PAU5</t>
+          <t>HXT10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YFL020C</t>
+          <t>YFL011W</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4823,16 +4823,16 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>PAU5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YFL040W</t>
+          <t>YFL020C</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4884,16 +4884,16 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>COS4</t>
+          <t>YFL040W</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>YFL062W</t>
+          <t>YFL040W</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4934,18 +4934,18 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4995,27 +4995,27 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CWH41</t>
+          <t>COS4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YGL027C</t>
+          <t>YFL062W</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5067,16 +5067,16 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AGA2</t>
+          <t>CWH41</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>YGL032C</t>
+          <t>YGL027C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5128,16 +5128,16 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MF(ALPHA)2</t>
+          <t>AGA2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>YGL089C</t>
+          <t>YGL032C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5189,16 +5189,16 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TPN1</t>
+          <t>MF(ALPHA)2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YGL186C</t>
+          <t>YGL089C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5250,16 +5250,16 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KEX1</t>
+          <t>TPN1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>YGL203C</t>
+          <t>YGL186C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5311,16 +5311,16 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COS12</t>
+          <t>KEX1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YGL263W</t>
+          <t>YGL203C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5372,16 +5372,16 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MUP1</t>
+          <t>COS12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>YGR055W</t>
+          <t>YGL263W</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5433,16 +5433,16 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VSB1</t>
+          <t>MUP1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>YGR125W</t>
+          <t>YGR055W</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5483,18 +5483,18 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5544,27 +5544,27 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SNG1</t>
+          <t>VSB1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>YGR197C</t>
+          <t>YGR125W</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5616,16 +5616,16 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HSV2</t>
+          <t>SNG1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>YGR223C</t>
+          <t>YGR197C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5651,7 +5651,7 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5666,27 +5666,27 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Strømhaug PE, et al. (2004) PMID:15155809</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TNA1</t>
+          <t>HSV2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>YGR260W</t>
+          <t>YGR223C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5712,7 +5712,7 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5727,27 +5727,27 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Strømhaug PE, et al. (2004) PMID:15155809</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SCW4</t>
+          <t>TNA1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>YGR279C</t>
+          <t>YGR260W</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5799,16 +5799,16 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BGL2</t>
+          <t>SCW4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>YGR282C</t>
+          <t>YGR279C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5860,16 +5860,16 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>COS6</t>
+          <t>BGL2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YGR295C</t>
+          <t>YGR282C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5921,7 +5921,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5971,27 +5971,27 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>COS6</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>YHL008C</t>
+          <t>YGR295C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6043,16 +6043,16 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MUP3</t>
+          <t>YHL008C</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YHL036W</t>
+          <t>YHL008C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6093,27 +6093,27 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ARN1</t>
+          <t>MUP3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>YHL040C</t>
+          <t>YHL036W</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6165,16 +6165,16 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>ARN1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>YHL042W</t>
+          <t>YHL040C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6226,16 +6226,16 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ARN2</t>
+          <t>YHL042W</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>YHL047C</t>
+          <t>YHL042W</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6287,16 +6287,16 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>COS8</t>
+          <t>ARN2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>YHL048W</t>
+          <t>YHL047C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6348,16 +6348,16 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CPR2</t>
+          <t>COS8</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>YHR057C</t>
+          <t>YHL048W</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6409,16 +6409,16 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ANS1</t>
+          <t>CPR2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>YHR126C</t>
+          <t>YHR057C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6470,16 +6470,16 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WSS1</t>
+          <t>ANS1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>YHR134W</t>
+          <t>YHR126C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6505,7 +6505,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6520,27 +6520,27 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2017-01-10</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Balakirev MY, et al. (2015) PMID:26349035</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DSE2</t>
+          <t>WSS1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>YHR143W</t>
+          <t>YHR134W</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6566,7 +6566,7 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6581,27 +6581,27 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2017-01-10</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Balakirev MY, et al. (2015) PMID:26349035</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>DSE2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>YHR173C</t>
+          <t>YHR143W</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6653,16 +6653,16 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SMN1</t>
+          <t>YHR173C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>YHR202W</t>
+          <t>YHR173C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6714,7 +6714,7 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -6764,27 +6764,27 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PHO12</t>
+          <t>SMN1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>YHR215W</t>
+          <t>YHR202W</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6836,16 +6836,16 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TIR3</t>
+          <t>PHO12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>YIL011W</t>
+          <t>YHR215W</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6886,27 +6886,27 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MNT3</t>
+          <t>TIR3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>YIL014W</t>
+          <t>YIL011W</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6958,16 +6958,16 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>MNT3</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>YIL067C</t>
+          <t>YIL014W</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7008,27 +7008,27 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AVT7</t>
+          <t>YIL067C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>YIL088C</t>
+          <t>YIL067C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7069,18 +7069,18 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7130,18 +7130,18 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -7191,27 +7191,27 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Nishida I, et al. (2016) PMID:27246536</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>AVT7</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>YIL089W</t>
+          <t>YIL088C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7237,7 +7237,7 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7252,27 +7252,27 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Nishida I, et al. (2016) PMID:27246536</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SGA1</t>
+          <t>YIL089W</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>YIL099W</t>
+          <t>YIL089W</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7298,7 +7298,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7313,18 +7313,18 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Pugh TA, et al. (1989) PMID:2493265</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7374,27 +7374,27 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Pugh TA, et al. (1989) PMID:2493265</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AXL2</t>
+          <t>SGA1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>YIL140W</t>
+          <t>YIL099W</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7446,16 +7446,16 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AIM20</t>
+          <t>AXL2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>YIL158W</t>
+          <t>YIL140W</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7496,27 +7496,27 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SUC2</t>
+          <t>AIM20</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>YIL162W</t>
+          <t>YIL158W</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7557,27 +7557,27 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SOA1</t>
+          <t>SUC2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>YIL166C</t>
+          <t>YIL162W</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7629,16 +7629,16 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VTH1</t>
+          <t>SOA1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>YIL173W</t>
+          <t>YIL166C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7690,16 +7690,16 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VLD1</t>
+          <t>VTH1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>YIR014W</t>
+          <t>YIL173W</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7740,27 +7740,27 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FLO11</t>
+          <t>VLD1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>YIR019C</t>
+          <t>YIR014W</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7801,27 +7801,27 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DAL4</t>
+          <t>FLO11</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>YIR028W</t>
+          <t>YIR019C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7873,16 +7873,16 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PAU15</t>
+          <t>DAL4</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>YIR041W</t>
+          <t>YIR028W</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7934,16 +7934,16 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IRC18</t>
+          <t>PAU15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>YJL037W</t>
+          <t>YIR041W</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7995,16 +7995,16 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>IRC8</t>
+          <t>IRC18</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>YJL051W</t>
+          <t>YJL037W</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8056,16 +8056,16 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>YHC3</t>
+          <t>IRC8</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>YJL059W</t>
+          <t>YJL051W</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8091,7 +8091,7 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8106,18 +8106,18 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Pearce DA, et al. (1999) PMID:10319861</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -8172,22 +8172,22 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Croopnick JB, et al. (1998) PMID:9753630</t>
+          <t>Pearce DA, et al. (1999) PMID:10319861</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PRY1</t>
+          <t>YHC3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>YJL079C</t>
+          <t>YJL059W</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8213,7 +8213,7 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8228,27 +8228,27 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Croopnick JB, et al. (1998) PMID:9753630</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PHS1</t>
+          <t>PRY1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>YJL097W</t>
+          <t>YJL079C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8274,7 +8274,7 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8289,18 +8289,18 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8350,18 +8350,18 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -8416,22 +8416,22 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Hazbun TR, et al. (2003) PMID:14690591</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NCA3</t>
+          <t>PHS1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>YJL116C</t>
+          <t>YJL097W</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8472,27 +8472,27 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Hazbun TR, et al. (2003) PMID:14690591</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>NCA3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>YJL132W</t>
+          <t>YJL116C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8544,16 +8544,16 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SNA3</t>
+          <t>YJL132W</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>YJL151C</t>
+          <t>YJL132W</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8579,7 +8579,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8594,18 +8594,18 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2014-01-21</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -8655,27 +8655,27 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2014-01-21</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Jarmoszewicz K, et al. (2012) PMID:22761830</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CIS3</t>
+          <t>SNA3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>YJL158C</t>
+          <t>YJL151C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8701,7 +8701,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8716,27 +8716,27 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PIR5</t>
+          <t>CIS3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>YJL160C</t>
+          <t>YJL158C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8788,16 +8788,16 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CPS1</t>
+          <t>PIR5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>YJL172W</t>
+          <t>YJL160C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8849,16 +8849,16 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>KRE9</t>
+          <t>CPS1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>YJL174W</t>
+          <t>YJL172W</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8910,16 +8910,16 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ATG27</t>
+          <t>KRE9</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>YJL178C</t>
+          <t>YJL174W</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8971,16 +8971,16 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HXT9</t>
+          <t>ATG27</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>YJL219W</t>
+          <t>YJL178C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9032,16 +9032,16 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VTH2</t>
+          <t>HXT9</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>YJL222W</t>
+          <t>YJL219W</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9093,16 +9093,16 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PAU1</t>
+          <t>VTH2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>YJL223C</t>
+          <t>YJL222W</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9154,16 +9154,16 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>AVT1</t>
+          <t>PAU1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>YJR001W</t>
+          <t>YJL223C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9189,7 +9189,7 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9204,18 +9204,18 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -9265,27 +9265,27 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Nishida I, et al. (2016) PMID:27246536</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAG1</t>
+          <t>AVT1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>YJR004C</t>
+          <t>YJR001W</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9311,7 +9311,7 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9326,27 +9326,27 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Nishida I, et al. (2016) PMID:27246536</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GEF1</t>
+          <t>SAG1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>YJR040W</t>
+          <t>YJR004C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9372,7 +9372,7 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9387,27 +9387,27 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>López-Rodríguez A, et al. (2007) PMID:17662057</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>KCH1</t>
+          <t>GEF1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>YJR054W</t>
+          <t>YJR040W</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9433,7 +9433,7 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9448,27 +9448,27 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>López-Rodríguez A, et al. (2007) PMID:17662057</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>URA8</t>
+          <t>KCH1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>YJR103W</t>
+          <t>YJR054W</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9509,27 +9509,27 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MET5</t>
+          <t>URA8</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>YJR137C</t>
+          <t>YJR103W</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9581,16 +9581,16 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DAL5</t>
+          <t>MET5</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>YJR152W</t>
+          <t>YJR137C</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9642,16 +9642,16 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MPH3</t>
+          <t>DAL5</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>YJR160C</t>
+          <t>YJR152W</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9703,16 +9703,16 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>COS5</t>
+          <t>MPH3</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>YJR161C</t>
+          <t>YJR160C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9753,27 +9753,27 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TUL1</t>
+          <t>COS5</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>YKL034W</t>
+          <t>YJR161C</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9814,27 +9814,27 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CWP1</t>
+          <t>TUL1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>YKL096W</t>
+          <t>YKL034W</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9886,16 +9886,16 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>APE1</t>
+          <t>CWP1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>YKL103C</t>
+          <t>YKL096W</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9921,7 +9921,7 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9936,27 +9936,27 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Klionsky DJ, et al. (1992) PMID:1400574</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SSH4</t>
+          <t>APE1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>YKL124W</t>
+          <t>YKL103C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -10002,22 +10002,22 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Kota J, et al. (2007) PMID:17287526</t>
+          <t>Klionsky DJ, et al. (1992) PMID:1400574</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AVT3</t>
+          <t>SSH4</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>YKL146W</t>
+          <t>YKL124W</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10058,27 +10058,27 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Nishida I, et al. (2016) PMID:27246536</t>
+          <t>Kota J, et al. (2007) PMID:17287526</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MCD4</t>
+          <t>AVT3</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>YKL165C</t>
+          <t>YKL146W</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10119,27 +10119,27 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Packeiser AN, et al. (1999) PMID:10514566</t>
+          <t>Nishida I, et al. (2016) PMID:27246536</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>YKT6</t>
+          <t>MCD4</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>YKL196C</t>
+          <t>YKL165C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10185,22 +10185,22 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Dietrich LE, et al. (2005) PMID:15723044</t>
+          <t>Packeiser AN, et al. (1999) PMID:10514566</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>STE6</t>
+          <t>YKT6</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>YKL209C</t>
+          <t>YKL196C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10226,7 +10226,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10241,27 +10241,27 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Dietrich LE, et al. (2005) PMID:15723044</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JEN1</t>
+          <t>STE6</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>YKL217W</t>
+          <t>YKL209C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10313,16 +10313,16 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>FRE2</t>
+          <t>JEN1</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>YKL220C</t>
+          <t>YKL217W</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10374,16 +10374,16 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PAU16</t>
+          <t>FRE2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>YKL224C</t>
+          <t>YKL220C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10435,16 +10435,16 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PRY2</t>
+          <t>PAU16</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>YKR013W</t>
+          <t>YKL224C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10485,27 +10485,27 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>UIP5</t>
+          <t>PRY2</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>YKR044W</t>
+          <t>YKR013W</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10546,27 +10546,27 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PTR2</t>
+          <t>UIP5</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>YKR093W</t>
+          <t>YKR044W</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10618,16 +10618,16 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PAU17</t>
+          <t>PTR2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>YLL025W</t>
+          <t>YKR093W</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10679,16 +10679,16 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FPS1</t>
+          <t>PAU17</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>YLL043W</t>
+          <t>YLL025W</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10729,18 +10729,18 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -10790,27 +10790,27 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>YBT1</t>
+          <t>FPS1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>YLL048C</t>
+          <t>YLL043W</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10836,7 +10836,7 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10851,27 +10851,27 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Ortiz DF, et al. (1997) PMID:9182565</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FRE6</t>
+          <t>YBT1</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>YLL051C</t>
+          <t>YLL048C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10897,7 +10897,7 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10912,18 +10912,18 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Ortiz DF, et al. (1997) PMID:9182565</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -10973,27 +10973,27 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>FRE6</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>YLR001C</t>
+          <t>YLL051C</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -11034,27 +11034,27 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PAU23</t>
+          <t>YLR001C</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>YLR037C</t>
+          <t>YLR001C</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11106,16 +11106,16 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NFG1</t>
+          <t>PAU23</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>YLR042C</t>
+          <t>YLR037C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11167,16 +11167,16 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>NFG1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>YLR046C</t>
+          <t>YLR042C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11228,16 +11228,16 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>LCL2</t>
+          <t>YLR046C</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>YLR104W</t>
+          <t>YLR046C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11289,16 +11289,16 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CCW12</t>
+          <t>LCL2</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>YLR110C</t>
+          <t>YLR104W</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11350,16 +11350,16 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>NCW2</t>
+          <t>CCW12</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>YLR194C</t>
+          <t>YLR110C</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11411,16 +11411,16 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CRR1</t>
+          <t>NCW2</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>YLR213C</t>
+          <t>YLR194C</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11472,16 +11472,16 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CCC1</t>
+          <t>CRR1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>YLR220W</t>
+          <t>YLR213C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11507,7 +11507,7 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11522,27 +11522,27 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SSP120</t>
+          <t>CCC1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>YLR250W</t>
+          <t>YLR220W</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11568,7 +11568,7 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11583,27 +11583,27 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CTS1</t>
+          <t>SSP120</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>YLR286C</t>
+          <t>YLR250W</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11655,16 +11655,16 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>CTS1</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>YLR297W</t>
+          <t>YLR286C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11705,27 +11705,27 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ECM38</t>
+          <t>YLR297W</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>YLR299W</t>
+          <t>YLR297W</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11751,7 +11751,7 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11766,27 +11766,27 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Jaspers CJ and Penninckx MJ (1984) PMID:6143574</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EXG1</t>
+          <t>ECM38</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>YLR300W</t>
+          <t>YLR299W</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11812,7 +11812,7 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11827,27 +11827,27 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Jaspers CJ and Penninckx MJ (1984) PMID:6143574</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MID2</t>
+          <t>EXG1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>YLR332W</t>
+          <t>YLR300W</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11899,16 +11899,16 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>GAS2</t>
+          <t>MID2</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>YLR343W</t>
+          <t>YLR332W</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11960,16 +11960,16 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DCR2</t>
+          <t>GAS2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>YLR361C</t>
+          <t>YLR343W</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -12021,16 +12021,16 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>VPS33</t>
+          <t>DCR2</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>YLR396C</t>
+          <t>YLR361C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12056,7 +12056,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12071,27 +12071,27 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>VPS33</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>YLR406C-A</t>
+          <t>YLR396C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12117,7 +12117,7 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12132,27 +12132,27 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>INA1</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>YLR413W</t>
+          <t>YLR406C-A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12204,16 +12204,16 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ECM7</t>
+          <t>INA1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>YLR443W</t>
+          <t>YLR413W</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12265,16 +12265,16 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PAU4</t>
+          <t>ECM7</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>YLR461W</t>
+          <t>YLR443W</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12326,16 +12326,16 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>YPT7</t>
+          <t>PAU4</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>YML001W</t>
+          <t>YLR461W</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12361,7 +12361,7 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12376,27 +12376,27 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ERV25</t>
+          <t>YPT7</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>YML012W</t>
+          <t>YML001W</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12422,7 +12422,7 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12437,27 +12437,27 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PRM6</t>
+          <t>ERV25</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>YML047C</t>
+          <t>YML012W</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12509,16 +12509,16 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SMA2</t>
+          <t>PRM6</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>YML066C</t>
+          <t>YML047C</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12570,16 +12570,16 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MDM1</t>
+          <t>SMA2</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>YML104C</t>
+          <t>YML066C</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12631,16 +12631,16 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PHO84</t>
+          <t>MDM1</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>YML123C</t>
+          <t>YML104C</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12692,16 +12692,16 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>COS3</t>
+          <t>PHO84</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>YML132W</t>
+          <t>YML123C</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12753,7 +12753,7 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -12803,18 +12803,18 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12864,27 +12864,27 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Mitsui K, et al. (2004) PMID:14718542</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HXT2</t>
+          <t>COS3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>YMR011W</t>
+          <t>YML132W</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12910,7 +12910,7 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12925,27 +12925,27 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Mitsui K, et al. (2004) PMID:14718542</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>FET3</t>
+          <t>HXT2</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>YMR058W</t>
+          <t>YMR011W</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12997,16 +12997,16 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>FET3</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>YMR155W</t>
+          <t>YMR058W</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -13058,16 +13058,16 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GAS3</t>
+          <t>YMR155W</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>YMR215W</t>
+          <t>YMR155W</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -13119,16 +13119,16 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FMP42</t>
+          <t>GAS3</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>YMR221C</t>
+          <t>YMR215W</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -13169,27 +13169,27 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ZRC1</t>
+          <t>FMP42</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>YMR243C</t>
+          <t>YMR221C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13215,7 +13215,7 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13230,27 +13230,27 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Li L and Kaplan J (1998) PMID:9712830</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>ZRC1</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>YMR244W</t>
+          <t>YMR243C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -13276,7 +13276,7 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -13291,27 +13291,27 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Li L and Kaplan J (1998) PMID:9712830</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YMR244W</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>YMR247W-A</t>
+          <t>YMR244W</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -13363,16 +13363,16 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HOR7</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>YMR251W-A</t>
+          <t>YMR247W-A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13424,16 +13424,16 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>HOR7</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>YMR272W-B</t>
+          <t>YMR251W-A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13485,16 +13485,16 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PRC1</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>YMR297W</t>
+          <t>YMR272W-B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13520,7 +13520,7 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -13535,18 +13535,18 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -13596,27 +13596,27 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>FET4</t>
+          <t>PRC1</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>YMR319C</t>
+          <t>YMR297W</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -13657,27 +13657,27 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SPO1</t>
+          <t>FET4</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>YNL012W</t>
+          <t>YMR319C</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13729,16 +13729,16 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>SPO1</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>YNL019C</t>
+          <t>YNL012W</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13790,16 +13790,16 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YNL019C</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>YNL058C</t>
+          <t>YNL019C</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13840,27 +13840,27 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>AQR1</t>
+          <t>YNL058C</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>YNL065W</t>
+          <t>YNL058C</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13901,27 +13901,27 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>AVT4</t>
+          <t>AQR1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>YNL101W</t>
+          <t>YNL065W</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13947,7 +13947,7 @@
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -13962,27 +13962,27 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Russnak R, et al. (2001) PMID:11274162</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>AVT4</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>YNL115C</t>
+          <t>YNL101W</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -14008,7 +14008,7 @@
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14023,27 +14023,27 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Russnak R, et al. (2001) PMID:11274162</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>NRK1</t>
+          <t>YNL115C</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>YNL129W</t>
+          <t>YNL115C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -14084,27 +14084,27 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TDA7</t>
+          <t>NRK1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>YNL176C</t>
+          <t>YNL129W</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -14145,18 +14145,18 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14206,27 +14206,27 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PPN2</t>
+          <t>TDA7</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>YNL217W</t>
+          <t>YNL176C</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -14252,7 +14252,7 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -14267,18 +14267,18 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -14328,27 +14328,27 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>KEX2</t>
+          <t>PPN2</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>YNL238W</t>
+          <t>YNL217W</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -14374,7 +14374,7 @@
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -14389,27 +14389,27 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>BOR1</t>
+          <t>KEX2</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>YNL275W</t>
+          <t>YNL238W</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14435,7 +14435,7 @@
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -14450,27 +14450,27 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Decker BL and Wickner WT (2006) PMID:16565073</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PRM1</t>
+          <t>BOR1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>YNL279W</t>
+          <t>YNL275W</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14496,7 +14496,7 @@
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -14511,27 +14511,27 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Decker BL and Wickner WT (2006) PMID:16565073</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>WSC2</t>
+          <t>PRM1</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>YNL283C</t>
+          <t>YNL279W</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14583,16 +14583,16 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>CLA4</t>
+          <t>WSC2</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>YNL298W</t>
+          <t>YNL283C</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14618,7 +14618,7 @@
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14633,27 +14633,27 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Bartholomew CR and Hardy CF (2009) PMID:19218422</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>BXI1</t>
+          <t>CLA4</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>YNL305C</t>
+          <t>YNL298W</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14679,7 +14679,7 @@
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14694,18 +14694,18 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Bartholomew CR and Hardy CF (2009) PMID:19218422</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -14755,18 +14755,18 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14816,18 +14816,18 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Büttner S, et al. (2011) PMID:21673659</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -14882,22 +14882,22 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Cebulski J, et al. (2011) PMID:21673967</t>
+          <t>Büttner S, et al. (2011) PMID:21673659</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HXT14</t>
+          <t>BXI1</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>YNL318C</t>
+          <t>YNL305C</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14923,7 +14923,7 @@
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14938,27 +14938,27 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Cebulski J, et al. (2011) PMID:21673967</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>HXT14</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>YNL320W</t>
+          <t>YNL318C</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -15010,16 +15010,16 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>VNX1</t>
+          <t>YNL320W</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>YNL321W</t>
+          <t>YNL320W</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -15045,7 +15045,7 @@
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -15060,27 +15060,27 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Cagnac O, et al. (2007) PMID:17588950</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>KRE1</t>
+          <t>VNX1</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>YNL322C</t>
+          <t>YNL321W</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -15106,7 +15106,7 @@
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -15121,27 +15121,27 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Cagnac O, et al. (2007) PMID:17588950</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PFA3</t>
+          <t>KRE1</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>YNL326C</t>
+          <t>YNL322C</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -15167,7 +15167,7 @@
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -15182,18 +15182,18 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Hou H, et al. (2005) PMID:16301533</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -15243,18 +15243,18 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Hou H, et al. (2005) PMID:16301533</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
-          <t>IMP</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -15304,18 +15304,18 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Hou H, et al. (2005) PMID:16301533</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IMP</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15365,27 +15365,27 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Hou H, et al. (2005) PMID:16301533</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>EGT2</t>
+          <t>PFA3</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>YNL327W</t>
+          <t>YNL326C</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -15437,16 +15437,16 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>COS1</t>
+          <t>EGT2</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>YNL336W</t>
+          <t>YNL327W</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15498,7 +15498,7 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -15548,27 +15548,27 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ATO2</t>
+          <t>COS1</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>YNR002C</t>
+          <t>YNL336W</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15609,27 +15609,27 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>CPR8</t>
+          <t>ATO2</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>YNR028W</t>
+          <t>YNR002C</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15670,27 +15670,27 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HOL1</t>
+          <t>CPR8</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>YNR055C</t>
+          <t>YNR028W</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15731,27 +15731,27 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>HOL1</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>YNR061C</t>
+          <t>YNR055C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15777,7 +15777,7 @@
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -15792,18 +15792,18 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -15853,27 +15853,27 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YNR061C</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>YNR066C</t>
+          <t>YNR061C</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15914,27 +15914,27 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HXT17</t>
+          <t>YNR066C</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>YNR072W</t>
+          <t>YNR066C</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15986,16 +15986,16 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PAU6</t>
+          <t>HXT17</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>YNR076W</t>
+          <t>YNR072W</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -16047,16 +16047,16 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>IZH2</t>
+          <t>PAU6</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>YOL002C</t>
+          <t>YNR076W</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -16108,16 +16108,16 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CSI2</t>
+          <t>IZH2</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>YOL007C</t>
+          <t>YOL002C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -16169,7 +16169,7 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -16219,18 +16219,18 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Sundin BA, et al. (2004) PMID:15282802</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -16280,27 +16280,27 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Sundin BA, et al. (2004) PMID:15282802</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PLB3</t>
+          <t>CSI2</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>YOL011W</t>
+          <t>YOL007C</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -16341,27 +16341,27 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>TOS7</t>
+          <t>PLB3</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>YOL019W</t>
+          <t>YOL011W</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -16402,27 +16402,27 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DDR2</t>
+          <t>TOS7</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>YOL052C-A</t>
+          <t>YOL019W</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16463,18 +16463,18 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -16524,27 +16524,27 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PHM7</t>
+          <t>DDR2</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>YOL084W</t>
+          <t>YOL052C-A</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -16596,16 +16596,16 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>IZH4</t>
+          <t>PHM7</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>YOL101C</t>
+          <t>YOL084W</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -16646,27 +16646,27 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ITR2</t>
+          <t>IZH4</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>YOL103W</t>
+          <t>YOL101C</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -16718,16 +16718,16 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>WSC3</t>
+          <t>ITR2</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>YOL105C</t>
+          <t>YOL103W</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16779,16 +16779,16 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SMF1</t>
+          <t>WSC3</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>YOL122C</t>
+          <t>YOL105C</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16840,16 +16840,16 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>GAS4</t>
+          <t>SMF1</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>YOL132W</t>
+          <t>YOL122C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16901,16 +16901,16 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>RTC1</t>
+          <t>GAS4</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>YOL138C</t>
+          <t>YOL132W</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16951,27 +16951,27 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ZPS1</t>
+          <t>RTC1</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>YOL154W</t>
+          <t>YOL138C</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -17023,16 +17023,16 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>ENB1</t>
+          <t>ZPS1</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>YOL158C</t>
+          <t>YOL154W</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -17073,27 +17073,27 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PAU20</t>
+          <t>ENB1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>YOL161C</t>
+          <t>YOL158C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -17145,16 +17145,16 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SLG1</t>
+          <t>PAU20</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>YOR008C</t>
+          <t>YOL161C</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -17206,16 +17206,16 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>TIR4</t>
+          <t>SLG1</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>YOR009W</t>
+          <t>YOR008C</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -17267,16 +17267,16 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TIR2</t>
+          <t>TIR4</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>YOR010C</t>
+          <t>YOR009W</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -17328,16 +17328,16 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>AKR2</t>
+          <t>TIR2</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>YOR034C</t>
+          <t>YOR010C</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -17389,16 +17389,16 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>RSB1</t>
+          <t>AKR2</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>YOR049C</t>
+          <t>YOR034C</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -17450,16 +17450,16 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>YVC1</t>
+          <t>RSB1</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>YOR087W</t>
+          <t>YOR049C</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17485,7 +17485,7 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -17500,18 +17500,18 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Palmer CP, et al. (2001) PMID:11427713</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -17566,22 +17566,22 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Denis V and Cyert MS (2002) PMID:11781332</t>
+          <t>Palmer CP, et al. (2001) PMID:11427713</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>KTR1</t>
+          <t>YVC1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>YOR099W</t>
+          <t>YOR087W</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -17607,7 +17607,7 @@
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -17622,27 +17622,27 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Denis V and Cyert MS (2002) PMID:11781332</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>RIO1</t>
+          <t>KTR1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>YOR119C</t>
+          <t>YOR099W</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -17668,7 +17668,7 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -17683,27 +17683,27 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2021-11-22</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Iacovella MG, et al. (2018) PMID:30011030</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SPR1</t>
+          <t>RIO1</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>YOR190W</t>
+          <t>YOR119C</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17729,7 +17729,7 @@
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -17744,27 +17744,27 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2021-11-22</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Iacovella MG, et al. (2018) PMID:30011030</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>THI72</t>
+          <t>SPR1</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>YOR192C</t>
+          <t>YOR190W</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17816,16 +17816,16 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SPR2</t>
+          <t>THI72</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>YOR214C</t>
+          <t>YOR192C</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -17877,16 +17877,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SRL1</t>
+          <t>SPR2</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>YOR247W</t>
+          <t>YOR214C</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17927,27 +17927,27 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>VPH1</t>
+          <t>SRL1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>YOR270C</t>
+          <t>YOR247W</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -17973,7 +17973,7 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -17988,27 +17988,27 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MPD1</t>
+          <t>VPH1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>YOR288C</t>
+          <t>YOR270C</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -18034,7 +18034,7 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -18049,27 +18049,27 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>MPD1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>YOR292C</t>
+          <t>YOR288C</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -18121,16 +18121,16 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>RAX1</t>
+          <t>YOR292C</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>YOR301W</t>
+          <t>YOR292C</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -18171,27 +18171,27 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>COT1</t>
+          <t>RAX1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>YOR316C</t>
+          <t>YOR301W</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -18217,7 +18217,7 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18232,27 +18232,27 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Li L and Kaplan J (1998) PMID:9712830</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PDR10</t>
+          <t>COT1</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>YOR328W</t>
+          <t>YOR316C</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -18278,7 +18278,7 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -18293,27 +18293,27 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Li L and Kaplan J (1998) PMID:9712830</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>FRE3</t>
+          <t>PDR10</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>YOR381W</t>
+          <t>YOR328W</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -18365,16 +18365,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>FIT2</t>
+          <t>FRE3</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>YOR382W</t>
+          <t>YOR381W</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18426,16 +18426,16 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>FIT3</t>
+          <t>FIT2</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>YOR383C</t>
+          <t>YOR382W</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18487,16 +18487,16 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>KTR6</t>
+          <t>FIT3</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>YPL053C</t>
+          <t>YOR383C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18548,16 +18548,16 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>SUR1</t>
+          <t>KTR6</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>YPL057C</t>
+          <t>YPL053C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -18609,16 +18609,16 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>RNY1</t>
+          <t>SUR1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>YPL123C</t>
+          <t>YPL057C</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -18644,7 +18644,7 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -18659,27 +18659,27 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>2014-01-22</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Shcherbik N (2013) PMID:24102742</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PEP4</t>
+          <t>RNY1</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>YPL154C</t>
+          <t>YPL123C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -18705,7 +18705,7 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -18720,18 +18720,18 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2014-01-22</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Shcherbik N (2013) PMID:24102742</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
@@ -18781,27 +18781,27 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PRM4</t>
+          <t>PEP4</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>YPL156C</t>
+          <t>YPL154C</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -18827,7 +18827,7 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -18842,27 +18842,27 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Matsumoto R, et al. (2013) PMID:23708375</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>SVS1</t>
+          <t>PRM4</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>YPL163C</t>
+          <t>YPL156C</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -18903,27 +18903,27 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>TRE1</t>
+          <t>SVS1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>YPL176C</t>
+          <t>YPL163C</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -18949,7 +18949,7 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -18964,18 +18964,18 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Stimpson HE, et al. (2006) PMID:16456538</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -19025,27 +19025,27 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Stimpson HE, et al. (2006) PMID:16456538</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>FLC1</t>
+          <t>TRE1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>YPL221W</t>
+          <t>YPL176C</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -19086,27 +19086,27 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>VMA11</t>
+          <t>FLC1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>YPL234C</t>
+          <t>YPL221W</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -19132,7 +19132,7 @@
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -19147,27 +19147,27 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Wang L, et al. (2002) PMID:11853670</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DIP5</t>
+          <t>VMA11</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>YPL265W</t>
+          <t>YPL234C</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -19193,7 +19193,7 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -19208,27 +19208,27 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Wang L, et al. (2002) PMID:11853670</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PAU22</t>
+          <t>DIP5</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>YPL282C</t>
+          <t>YPL265W</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -19280,16 +19280,16 @@
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ATH1</t>
+          <t>PAU22</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>YPR026W</t>
+          <t>YPL282C</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -19315,7 +19315,7 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
-          <t>IMP</t>
+          <t>HDA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
@@ -19330,27 +19330,27 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2013-08-07</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Destruelle M, et al. (1995) PMID:7502577</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>ERV2</t>
+          <t>ATH1</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>YPR037C</t>
+          <t>YPR026W</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -19376,7 +19376,7 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
-          <t>HDA</t>
+          <t>IMP</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
@@ -19391,27 +19391,27 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2013-08-07</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Destruelle M, et al. (1995) PMID:7502577</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>OPY2</t>
+          <t>ERV2</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>YPR075C</t>
+          <t>YPR037C</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -19452,27 +19452,27 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2018-11-19</t>
+          <t>2018-11-20</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Huh WK, et al. (2003) PMID:14562095</t>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>TDA6</t>
+          <t>OPY2</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>YPR157W</t>
+          <t>YPR075C</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -19513,27 +19513,27 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2018-11-20</t>
+          <t>2018-11-19</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Yofe I, et al. (2016) PMID:26928762</t>
+          <t>Huh WK, et al. (2003) PMID:14562095</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>OPT2</t>
+          <t>TDA6</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>YPR194C</t>
+          <t>YPR157W</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -19578,6 +19578,67 @@
         </is>
       </c>
       <c r="M314" t="inlineStr">
+        <is>
+          <t>Yofe I, et al. (2016) PMID:26928762</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>323</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>OPT2</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>YPR194C</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>located in</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>GO:0000324</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>fungal-type vacuole</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>cellular component</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>HDA</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>manually curated</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2018-11-20</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
         <is>
           <t>Yofe I, et al. (2016) PMID:26928762</t>
         </is>
